--- a/제노사가 데이터베이스.xlsx
+++ b/제노사가 데이터베이스.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdaa27b0a01044acb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd69d7c15771a4d85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3941,10 +3941,8 @@
           <x:t xml:space="preserve">0xf50f|　元&lt;ヴェクター・インダストリー&gt;&lt;第一開発局&gt;、&lt;KOS-MOS&gt;開発計画統合オペレーションシステム開発室主任。\n\n　T.C.4763、18歳でヴェクター第一開発局に入局。&lt;アレン&gt;より2歳年下だが、飛び級のため、ヴェクターでは1年先輩にあたる。\n\n　&lt;グノーシス・テロ&gt;後、ヴェクターを退社してからは、&lt;スキエンティア&gt;にその身を置き、U.M.N.に潜在する危険性、そして一連の事件の背後に存在する真実を追究していた。\n\n　知るものは少ないが、先天的に特殊な知覚を持っており、幼い頃から常人には見えるはずのない虚数領域側が見えてしまうという特異な症状を抱えていた。シオンが日頃かけているホログラスは眼鏡ではなく、この症状の矯正用としてヴェクター時代に&lt;ケビン&gt;からプレゼントされた物である。コンタクトレンズにも同様の矯正機能が付いているらしい。\n\n　ただし常時その症状が出ている訳ではなく、彼女自身もそれに“慣れてしまっている”ため、日常生活に不便が無いときは外しているようである。\n\n　&lt;ロスト・エルサレム&gt;時代から彼女の意識は存在しており、&lt;巫女&gt;として、当時&lt;マリア&gt;とは親しい関係にあった。劇中彼女が垣間見た太古の風景は、KOS-MOSの記憶ではなく、彼女自身が見て体験したものである。\n\n　KOS-MOSの最後の台詞から、当時のシオンが何らかの事件に巻き込まれ命を落としたこと、そしてKOS-MOS（マリア）がそれからシオンを護れなかったことが推測出来る。\n\n　ミクタムにおいてアレンの想いに気付いたシオンは、自立への道の一歩を踏み出す。ケビンの存在があまりにも大きすぎたが故、それまでアレンの想いに気付いていなかったシオンだが、彼女にとって同じような境遇を持つケビンよりも、むしろ自分とは正反対の世界に生きているアレンこそ、心の安らぎの場を与えてくれる存在と言えるのではないだろうか。\n\n　ロスト・エルサレムへと旅立った者。曙光に残り、世界を再建しようとしている者。何千年、何万年にもわたる永久の旅路の果て。数多の意識が交叉するその刻。そこで彼らを待つものは──</x:t>
         </x:is>
       </x:c>
-      <x:c r="B303" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0xf50f|　전 &lt;벡터 인더스트리&gt; &lt;제1 개발국&gt;, &lt;KOS-MOS&gt; 개발 계획 통합 오퍼레이션 시스템 개발실 주임.\n\n　T.C. 4763, 18세의 나이에 벡터 제1 개발국에 입사했다. &lt;알렌&gt;보다 2살 어리지만 월반을 했기에 벡터에서는 1년 선배에 해당한다.\n\n　&lt;그노시스 테러&gt; 이후 벡터를 퇴사한 뒤로는 &lt;스키엔티아&gt;에 몸을 담고, U.M.N.에 잠재된 위험성, 그리고 일련의 사건의 배후에 존재하는 진실을 추구하고 있었다.\n\n　아는 이는 적으나, 선천적으로 특수한 지각 능력을 갖추고 있어 어린 시절부터 보통 사람에게는 보일 리 없는 허수 영역이 보이는 특이한 증상을 앓고 있었다. 시온이 평소 쓰고 다니는 홀로글래스는 안경이 아니라, 이 증상의 교정용으로 벡터 시절 &lt;케빈&gt;에게 선물받은 것이다. 콘택트렌즈에도 동일한 교정 기능이 들어 있는 듯하다.\n\n　단, 항상 그 증상이 나타나는 것은 아니며 그녀 자신도 그것에 “익숙해져” 있기에, 일상생활에 불편함이 없을 때는 벗어 두는 것 같다.\n\n　&lt;로스트 예루살렘&gt; 시대부터 그녀의 의식은 존재하고 있었으며, &lt;무녀&gt;로서 당시 &lt;마리아&gt;와 친밀한 관계였다. 극 중 그녀가 엿보았던 태고의 풍경은 KOS-MOS의 기억이 아니라, 그녀 자신이 직접 보고 체험한 것이다.\n\n　KOS-MOS의 마지막 대사로 미루어 볼 때, 당시의 시온이 어떠한 사건에 휘말려 목숨을 잃었다는 것, 그리고 KOS-MOS(마리아)가 그때 시온을 지켜 주지 못했다는 것을 추측할 수 있다.\n\n　믹담에서 알렌의 마음을 깨달은 시온은 자립을 향한 길의 첫발을 내디딘다. 케빈의 존재가 너무나 컸기에 그때까지 알렌의 마음을 눈치채지 못했던 시온이지만, 그녀에게 있어 같은 처지를 공유하는 케빈보다 오히려 자신과는 정반대의 세계에서 살아가는 알렌이야말로 마음의 안식처를 주는 존재라고 할 수 있지 않을까.\n\n　로스트 예루살렘으로 떠난 자들. 아침놀 속에 남아 세계를 재건하려는 자들. 수천 년, 수만 년에 걸친 영구한 여정의 끝. 수많은 의식이 교차하는 그 순간. 그곳에서 그들을 기다리는 것은──</x:t>
-        </x:is>
+      <x:c r="B303" t="str">
+        <x:v>0xf50f|　전 &lt;벡터 인더스트리&gt; &lt;제1 개발국&gt;, &lt;KOS-MOS&gt; 개발 계획 통합 오퍼레이션 시스템 개발실 주임.\n\n　T.C. 4763, 18세의 나이에 벡터 제1 개발국에 입사했다. &lt;알렌&gt;보다 2살 어리지만 월반을 했기에 벡터에서는 1년 선배에 해당한다.\n\n　&lt;그노시스 테러&gt; 이후 벡터를 퇴사한 뒤로는 &lt;스키엔티아&gt;에 몸을 담고, U.M.N.에 잠재된 위험성, 그리고 일련의 사건의 배후에 존재하는 진실을 추구하고 있었다.\n\n　아는 이는 적으나, 선천적으로 특수한 지각 능력을 갖추고 있어 어린 시절부터 보통 사람에게는 보일 리 없는 허수 영역이 보이는 특이한 증상을 앓고 있었다. 시온이 평소 쓰고 다니는 홀로글라스는 안경이 아니라, 이 증상의 교정용으로 벡터 시절 &lt;케빈&gt;에게 선물받은 것이다. 콘택트렌즈에도 동일한 교정 기능이 들어 있는 듯하다.\n\n　단, 항상 그 증상이 나타나는 것은 아니며 그녀 자신도 그것에 “익숙해져” 있기에, 일상생활에 불편함이 없을 때는 벗어 두는 것 같다.\n\n　&lt;로스트 예루살렘&gt; 시대부터 그녀의 의식은 존재하고 있었으며, &lt;무녀&gt;로서 당시 &lt;마리아&gt;와 친밀한 관계였다. 극 중 그녀가 엿보았던 태고의 풍경은 KOS-MOS의 기억이 아니라, 그녀 자신이 직접 보고 체험한 것이다.\n\n　KOS-MOS의 마지막 대사로 미루어 볼 때, 당시의 시온이 어떠한 사건에 휘말려 목숨을 잃었다는 것, 그리고 KOS-MOS(마리아)가 그때 시온을 지켜 주지 못했다는 것을 추측할 수 있다.\n\n　믹담에서 알렌의 마음을 깨달은 시온은 자립을 향한 길의 첫발을 내디딘다. 케빈의 존재가 너무나 컸기에 그때까지 알렌의 마음을 눈치채지 못했던 시온이지만, 그녀에게 있어 같은 처지를 공유하는 케빈보다 오히려 자신과는 정반대의 세계에서 살아가는 알렌이야말로 마음의 안식처를 주는 존재라고 할 수 있지 않을까.\n\n　로스트 예루살렘으로 떠난 자들. 아침놀 속에 남아 세계를 재건하려는 자들. 수천 년, 수만 년에 걸친 영구한 여정의 끝. 수많은 의식이 교차하는 그 순간. 그곳에서 그들을 기다리는 것은──</x:v>
       </x:c>
     </x:row>
     <x:row r="304">
@@ -5069,10 +5067,8 @@
           <x:t xml:space="preserve">0x122df|　惑星ブレッザ出身の若者。\n\n　ロスト・エルサレム時代のレトロアンティークに憧れて&lt;クーカイ・ファウンデーション&gt;に旅行に来たが、あまりの居心地の良さにそのまま居座ってしまう。\n\n　その後、バー『アイアン・マン』で同席した老人と意気投合し&lt;ロボットアカデミー&gt;に住みつき、その老人&lt;ハカセ&gt;の助手として&lt;巨大ロボット&gt;の研究に明け暮れる毎日を過ごす。おっとりした外見に似合わず大のお酒好き。  </x:t>
         </x:is>
       </x:c>
-      <x:c r="B397" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0x122df|　행성 브레차 출신의 청년.\n\n　로스트 예루살렘 시대의 레트로 앤티크를 동경하여 &lt;쿠카이 파운데이션&gt;으로 여행을 왔지만, 너무나 편안한 나머지 그대로 눌러앉아 버린다.\n\n　그 후 술집 『아이언 맨』에서 합석한 노인과 의기투합하여 &lt;로봇 아카데미&gt;에 머무르며, 그 노인 &lt;박사&gt;의 조수로서 &lt;거대 로봇&gt; 연구에 몰두하는 나날을 보내고 있다. 얌전한 외모와는 달리 엄청난 애주가.</x:t>
-        </x:is>
+      <x:c r="B397" t="str">
+        <x:v>0x122df|　행성 브레차 출신의 청년.\n\n　로스트 예루살렘 시대의 레트로 앤티크를 동경하여 &lt;쿠카이 파운데이션&gt;으로 여행을 왔지만, 너무나 편안한 나머지 그대로 눌러앉아 버린다.\n\n　그 후 술집 『아이언맨』에서 합석한 노인과 의기투합하여 &lt;로봇 아카데미&gt;에 머무르며, 그 노인 &lt;박사&gt;의 조수로서 &lt;거대 로봇&gt; 연구에 몰두하는 나날을 보내고 있다. 얌전한 외모와는 달리 엄청난 애주가.</x:v>
       </x:c>
     </x:row>
     <x:row r="398">
@@ -23689,10 +23685,8 @@
           <x:t xml:space="preserve">0x3894c|　『Anti Gnosis Weapon System』の略でエイグスと読む。\n\n　搭乗兵器だがその形態は人型に限らず、実態を持たない&lt;グノーシス&gt;と闘うために、様々な状況に対応したA.G.W.S.が開発されている。\n\n　主要稼動機関は転送型&lt;ジェネレーター&gt;であり、そのエネルギーの全ては母艦、または母機からの直接転送によって賄われる。よって、稼動時間に制限が無い。\n\n　現在、軍やU-TIC機関などに向けて量産されているのは、&lt;ハイアムズ重工&gt;製の&lt;AGシリーズ&gt;で、&lt;ヴェクター・インダストリー&gt;製の&lt;VXシリーズ&gt;は、AGシリーズをスペック的には上回るものの、民間への販売を視野に入れているため、現在は政府の特殊機関や軍の一部隊での試験運用に止まっている。</x:t>
         </x:is>
       </x:c>
-      <x:c r="B1949" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0x3894c|　『Anti Gnosis Weapon System』의 약자로 에이구스라 읽는다.\n\n　탑승 병기이지만 그 형태는 인간형에 국한되지 않으며, 실체가 없는 &lt;그노시스&gt;와 싸우기 위해 다양한 상황에 대응하는 A.G.W.S.가 개발되고 있다.\n\n　주요 가동 기관은 전송형 &lt;제너레이터&gt;이며 그 에너지 전체는 모함 또는 모기체로부터 직접 전송을 통해 충당된다. 따라서 가동 시간에 제한이 없다.\n\n　현재 군이나 U-TIC 기관 등을 대상으로 양산되고 있는 것은 &lt;하이암즈 중공&gt;제의 &lt;AG 시리즈&gt;이며, &lt;벡터 인더스트리&gt;제의 &lt;VX 시리즈&gt;는 AG 시리즈를 스펙상으로는 능가하지만 민간 판매를 염두에 두고 있기 때문에 현재는 정부 특수 기관이나 군 일부 부대에서의 시험 운용에 그치고 있다.</x:t>
-        </x:is>
+      <x:c r="B1949" t="str">
+        <x:v>0x3894c|　『Anti Gnosis Weapon System』의 약자로 에이그스라 읽는다.\n\n　탑승 병기이지만 그 형태는 인간형에 국한되지 않으며, 실체가 없는 &lt;그노시스&gt;와 싸우기 위해 다양한 상황에 대응하는 A.G.W.S.가 개발되고 있다.\n\n　주요 가동 기관은 전송형 &lt;제너레이터&gt;이며 그 에너지 전체는 모함 또는 모기체로부터 직접 전송을 통해 충당된다. 따라서 가동 시간에 제한이 없다.\n\n　현재 군이나 U-TIC 기관 등을 대상으로 양산되고 있는 것은 &lt;하이암즈 중공&gt;제의 &lt;AG 시리즈&gt;이며, &lt;벡터 인더스트리&gt;제의 &lt;VX 시리즈&gt;는 AG 시리즈를 스펙상으로는 능가하지만 민간 판매를 염두에 두고 있기 때문에 현재는 정부 특수 기관이나 군 일부 부대에서의 시험 운용에 그치고 있다.</x:v>
       </x:c>
     </x:row>
     <x:row r="1950">
@@ -31177,10 +31171,8 @@
           <x:t xml:space="preserve">0x47667|　&lt;アニマの器&gt;が搭載された人型機動兵器の総称。\n\n　コクピットは単座型と複座型の二種類があり、その違いはパイロットとコ・パイロットを分けて火器管制をする必要があるかないかで、多数の火器が装備された機体のほとんどは複座型となっている。オルムスの機体は機能特化されているため、単座型となっている。\n\n　E.S.の機体サイズ自体は標準的なA.M.W.S.と大差はないが、その戦闘力は桁違いのものがあり、武装とパイロットの組み合わせによってはA.M.W.S.一個師団に匹敵するだけの戦闘力を秘めている。\n\n　最たる理由として挙げられるのが、稼働に必要なエネルギーの質とその供給方法が全く異なっている点であろう。A.M.W.S.はA.G.W.S.同様、母艦からのパルスエネルギー転送で稼働しており、それはU.M.N.との通信状況や、母艦の状態に大きく依存し、必然的に単位時間あたりのエネルギー供給量は限定されてしまう傾向にある。\n\n　特に戦闘によって母艦が轟沈してしまうと、基本的には内蔵コンデンサや補器として搭載されているコジェネレーターで稼働するより他に方法がなくなってしまう。しかし、搭載されている火器やロジカルドライブなどは、あくまでも母艦からの高パルスエネルギー供給を受けることを前提として設計されているため、それらをフルスペックで稼働させることは不可能となってしまう。\n\n　対してE.S.のそれは、アニマの器を仲立ちとして&lt;ゾハル&gt;からのエネルギー供給を受けて稼働しているため、原理的にその供給量は無限であり、また母艦の状態にも場所にも依存しないので、その戦闘行動半径や武装には事実上制限がない（もっとも機体のマスバランスや機動力を大幅に低減させるような度を超した巨大な武装が使用されるケースは希だが）。\n\n　ただし、アニマの器をゾハルとリンケージさせるには、搭乗者にその適性がないと不可能で（要するに起動させる事すら出来ない）、また適性者の数も星団全体でもごく少数である事から、自然とその運用は戦術レベルのものに限定されているようである。</x:t>
         </x:is>
       </x:c>
-      <x:c r="B2573" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0x47667|　&lt;아니마의 그릇&gt;이 탑재된 인간형 기동 병기의 총칭.\n\n　콕핏은 단좌형과 복좌형 2종류가 있다. 종류 선택은 파일럿과 코파일럿을 나누어 화기 관제를 할 필요가 있는지에 달렸으며, 다수의 화기가 장착된 기체는 대부분 복좌형이다. 오르무스의 기체는 기능이 특화되어 있기 때문에 단좌형이다.\n\n　E.S.의 기체 크기 자체는 표준적인 A.M.W.S.와 큰 차이가 없으나 그 전투력은 차원이 다르며, 무장과 파일럿의 조합에 따라서는 A.M.W.S. 1개 사단에 필적하는 전투력을 품을 수 있다.\n\n　가장 큰 이유로 꼽히는 것이 가동에 필요한 에너지의 질과 그 공급 방법이 완전히 다르다는 점이다. A.M.W.S.는 A.G.W.S.와 마찬가지로 모함으로부터의 펄스 에너지 전송으로 가동되며, 이는 U.M.N.과의 통신 상황이나 모함의 상태에 크게 의존하여 필연적으로 단위 시간당 에너지 공급량이 한정되는 경향이 있다.\n\n　특히 전투로 인해 모함이 격침되면 기본적으로 내장 콘덴서나 보조 기기로 탑재된 코제너레이터로 가동하는 수밖에 없게 된다. 하지만 탑재된 화기나 로지컬 드라이브 등은 어디까지나 모함으로부터의 고펄스 에너지 공급을 전제로 설계되었기 때문에, 이들을 풀 스펙으로 가동하는 것은 불가능해진다.\n\n　반면 E.S.의 경우, 아니마의 그릇을 매개로 &lt;조하르&gt;로부터 에너지 공급을 받아 가동하기 때문에 원리상 그 공급량은 무한하며, 모함의 상태나 장소에도 의존하지 않으므로 그 전투 행동 반경이나 무장에는 사실상 제한이 없다(물론 기체의 매스 밸런스나 기동력을 대폭 저하시킬 정도로 도를 넘은 거대한 무장이 사용되는 케이스는 드물지만).\n\n　다만 아니마의 그릇을 조하르와 링케이지시키려면 탑승자에게 그 적성이 없으면 불가능하며(요컨대 기동조차 할 수 없다), 적성자의 수 또한 성단 전체를 통틀어도 극소수이기 때문에 자연히 그 운용은 전술적 수준으로 한정되어 있는 듯하다.</x:t>
-        </x:is>
+      <x:c r="B2573" t="str">
+        <x:v>0x47667|　&lt;아니마의 그릇&gt;이 탑재된 인간형 기동 병기의 총칭.\n\n　콕핏은 단좌형과 복좌형 2종류가 있다. 종류 선택은 파일럿과 코파일럿을 나누어 화기 관제를 할 필요가 있는지에 달렸으며, 다수의 화기가 장착된 기체는 대부분 복좌형이다. 오르무스의 기체는 기능이 특화되어 있기 때문에 단좌형이다.\n\n　E.S.의 기체 크기 자체는 표준적인 A.M.W.S.와 큰 차이가 없으나 그 전투력은 차원이 다르며, 무장과 파일럿의 조합에 따라서는 A.M.W.S. 1개 사단에 필적하는 전투력을 품을 수 있다.\n\n　가장 큰 이유로 꼽히는 것이 가동에 필요한 에너지의 질과 그 공급 방법이 완전히 다르다는 점이다. A.M.W.S.는 A.G.W.S.와 마찬가지로 모함으로부터의 펄스 에너지 전송으로 가동되며, 이는 U.M.N.과의 통신 상황이나 모함의 상태에 크게 의존하여 필연적으로 단위 시간당 에너지 공급량이 한정되는 경향이 있다.\n\n　특히 전투로 인해 모함이 격침되면 기본적으로 내장 콘덴서나 보조 기기로 탑재된 코제너레이터로 가동하는 수밖에 없게 된다. 하지만 탑재된 화기나 로지컬 드라이브 등은 어디까지나 모함으로부터의 고펄스 에너지 공급을 전제로 설계되었기 때문에, 이들을 풀 스펙으로 가동하는 것은 불가능해진다.\n\n　반면 E.S.의 경우, 아니마의 그릇을 매개로 &lt;조하르&gt;로부터 에너지 공급을 받아 가동하기 때문에 원리상 그 공급량은 무한하며, 모함의 상태나 장소에도 의존하지 않으므로 그 전투 행동 반경이나 무장에는 사실상 제한이 없다(물론 기체의 매스 밸런스나 기동력을 대폭 저하시킬 정도로 도를 넘은 거대한 무장이 사용되는 케이스는 드물지만).\n\n　다만 아니마의 그릇을 조하르와 링키지시키려면 탑승자에게 그 적성이 없으면 불가능하며(요컨대 기동조차 할 수 없다), 적성자의 수 또한 성단 전체를 통틀어도 극소수이기 때문에 자연히 그 운용은 전술적 수준으로 한정되어 있는 듯하다.</x:v>
       </x:c>
     </x:row>
     <x:row r="2574">
@@ -39199,10 +39191,8 @@
           <x:t xml:space="preserve">0x573d7|　A.D.20XX、ケニア北部に位置するトゥルカナ湖畔で行われた発掘調査によって謎のプレート状の物体が発見された。後に“ゾハル”と呼称されるその物体により、ロスト・エルサレムはこの世界から消滅する事となり、人類は宇宙への脱出を余儀なくされた。\n\n　それから4000年後の現在。\n\n　T.C.4767、巡洋艦ヴォークリンデを旗艦とする星団連邦軍第一一七海兵隊は惑星アリアドネ消滅事件の調査隊護衛の任務に就いていた。\n\n　ヴォークリンデには、謎の敵性体“グノーシス”の襲撃に備えてヴェクター製の対グノーシス用アンドロイド\n“KOS-MOS”が緊急配備されており、その起動実験のために、ヴェクター第一開発局主任シオン・ウヅキを含む開発メンバーらも乗艦していた。\n\n　艦隊の調査任務が進行する中、KOS-MOSの起動実験が繰り返されるも、思うように捗らず、とても実戦を行える状態ではなかった。\n\n　実験の失敗に悩む一方、今は亡き恋人“ケビン”の忘れ形見ともいえるKOS-MOSが兵器として目覚める事に対し抵抗を感じるシオン。\n\n　副主任のアレン・リッジリーは、その彼女に思いを寄せ、絶えず心に掛けてはいたが、黙って見守ることしかできないでいた。\n\n　事件の起きた宙域の調査中、ヴォークリンデは“ゾハル”と思われる物体を発見、回収する。\n\n　調査を終え、宙域から離脱する艦隊。無事任務が終了した事に対し、安堵する艦隊クルー達。だがその直後、ゾハルを狙う“グノーシス”の大群が、艦隊を襲撃するのだった。\n\n　艦内に侵入したグノーシスに襲われるシオン。薄れゆく意識の中で、彼女は謎の少女“ネピリム”の幻を見る。\n\n　抵抗する力さえ無く、自らの死を覚悟するシオン。その彼女の危機を救ったのは、自律起動したKOS-MOSであった。\n\n　KOS-MOSの助けを受け、アレンやバージル達と合流したシオンは、そのままヴォークリンデからの脱出を試みる。\n\n　次々と襲い掛かるグノーシスを、易々と撃退していく\nKOS-MOS。だがその戦闘中、KOS-MOSはシオンの命を救うためにグノーシスと共にバージル中尉を射殺してしまう。\n\n　バージルを殺した事に、何の感情も抱かないKOS-MOSはその行為を非難するシオンに対し、自らを兵器だと言い放つ。\n\n　そんなKOS-MOSに、シオンはやりきれない思いを抱いたまま、アレン達と共に、救命艇でヴォークリンデを脱出するのだった。</x:t>
         </x:is>
       </x:c>
-      <x:c r="B3245" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0x573d7|　A.D. 20XX, 케냐 북부에 위치한 투르카나 호숫가에서 행해진 발굴 조사를 통해 수수께끼의 플레이트 형태를 한 물체가 발견되었다. 훗날 “조하르”라고 호칭되는 그 물체로 인해 로스트 예루살렘은 이 세계에서 소멸하게 되었고 인류는 우주로 탈출할 수밖에 없었다.\n\n　그로부터 4000년이 지난 현재.\n\n　T.C. 4767, 순양함 보클린데를 기함으로 하는 성단 연방군 제117 해병대는 행성 아리아드네 소실 사건 조사단의 호위 임무를 맡고 있었다.\n\n　보클린데에는 수수께끼의 적 “그노시스”의 습격에 대비해 벡터사에서 제조된 대그노시스용 안드로이드 “KOS-MOS”가 긴급 배치되어 있었으며, 그 기동 실험을 위해 벡터 제1 개발국 주임 시온 우즈키를 포함한 개발 멤버들도 승선해 있었다.\n\n　함대의 조사 임무가 진행되는 가운데 KOS-MOS의 기동 실험이 반복되지만 뜻대로 진척되지 않아 도저히 실전을 치를 수 있는 상태가 아니었다.\n\n　실험 실패로 고민하는 한편, 이제는 세상을 떠난 연인 “케빈”의 유품이나 다름없는 KOS-MOS가 병기로서 깨어나는 것에 거부감을 느끼는 시온.\n\n　부주임인 알렌 리즐리는 그런 그녀를 짝사랑하며 끊임없이 신경 쓰고 있었으나 그저 묵묵히 지켜볼 수밖에 없었다.\n\n　사건이 발생한 우주 영역을 조사하던 중 보클린데는 “조하르”로 추정되는 물체를 발견하고 회수한다.\n\n　조사를 마치고 우주 영역을 이탈하는 함대. 무사히 임무가 종료된 것에 안도하는 함대 크루들. 하지만 그 직후 조하르를 노리는 “그노시스” 대군이 함대를 습격한다.\n\n　함내에 침입한 그노시스에게 습격당하는 시온. 희미해지는 의식 속에서 그녀는 수수께끼의 소녀 “네피림”의 환영을 본다.\n\n　저항할 힘조차 없이 자신의 죽음을 각오하는 시온. 그런 그녀의 위기를 구한 것은 자율 기동한 KOS-MOS였다.\n\n　KOS-MOS의 도움을 받아 알렌, 버질 일행과 합류한 시온은 그대로 보클린데 탈출을 시도한다.\n\n　차례차례 덤벼드는 그노시스를 가볍게 격퇴하는 KOS-MOS. 하지만 그 전투 중 KOS-MOS는 시온의 목숨을 구하기 위해 그노시스와 함께 버질 중위를 사살하고 만다.\n\n　버질을 죽인 것에 아무런 감정도 느끼지 않는 KOS-MOS는 그 행위를 비난하는 시온을 향해 자신은 병기일 뿐이라고 일축한다.\n\n　그런 KOS-MOS에게 시온은 착잡한 마음을 품은 채 알렌 일행과 함께 구명정으로 보클린데를 탈출한다.</x:t>
-        </x:is>
+      <x:c r="B3245" t="str">
+        <x:v>0x573d7|　A.D. 20XX, 케냐 북부에 위치한 투르카나 호숫가에서 행해진 발굴 조사를 통해 수수께끼의 플레이트 형태를 한 물체가 발견되었다. 훗날 “조하르”라고 호칭되는 그 물체로 인해 로스트 예루살렘은 이 세계에서 소멸하게 되었고 인류는 우주로 탈출할 수밖에 없었다.\n\n　그로부터 4000년이 지난 현재.\n\n　T.C. 4767, 순양함 보클린데를 기함으로 하는 성단 연방군 제117 해병 사단는 행성 아리아드네 소실 사건 조사단의 호위 임무를 맡고 있었다.\n\n　보클린데에는 수수께끼의 적 “그노시스”의 습격에 대비해 벡터사에서 제조된 대그노시스용 안드로이드 “KOS-MOS”가 긴급 배치되어 있었으며, 그 기동 실험을 위해 벡터 제1 개발국 주임 시온 우즈키를 포함한 개발 멤버들도 승선해 있었다.\n\n　함대의 조사 임무가 진행되는 가운데 KOS-MOS의 기동 실험이 반복되지만 뜻대로 진척되지 않아 도저히 실전을 치를 수 있는 상태가 아니었다.\n\n　실험 실패로 고민하는 한편, 이제는 세상을 떠난 연인 “케빈”의 유품이나 다름없는 KOS-MOS가 병기로서 깨어나는 것에 거부감을 느끼는 시온.\n\n　부주임인 알렌 리즐리는 그런 그녀를 짝사랑하며 끊임없이 신경 쓰고 있었으나 그저 묵묵히 지켜볼 수밖에 없었다.\n\n　사건이 발생한 우주 영역을 조사하던 중 보클린데는 “조하르”로 추정되는 물체를 발견하고 회수한다.\n\n　조사를 마치고 우주 영역을 이탈하는 함대. 무사히 임무가 종료된 것에 안도하는 함대 크루들. 하지만 그 직후 조하르를 노리는 “그노시스” 대군이 함대를 습격한다.\n\n　함내에 침입한 그노시스에게 습격당하는 시온. 희미해지는 의식 속에서 그녀는 수수께끼의 소녀 “네피림”의 환영을 본다.\n\n　저항할 힘조차 없이 자신의 죽음을 각오하는 시온. 그런 그녀의 위기를 구한 것은 자율 기동한 KOS-MOS였다.\n\n　KOS-MOS의 도움을 받아 알렌, 버질 일행과 합류한 시온은 그대로 보클린데 탈출을 시도한다.\n\n　차례차례 덤벼드는 그노시스를 가볍게 격퇴하는 KOS-MOS. 하지만 그 전투 중 KOS-MOS는 시온의 목숨을 구하기 위해 그노시스와 함께 버질 중위를 사살하고 만다.\n\n　버질을 죽인 것에 아무런 감정도 느끼지 않는 KOS-MOS는 그 행위를 비난하는 시온을 향해 자신은 병기일 뿐이라고 일축한다.\n\n　그런 KOS-MOS에게 시온은 착잡한 마음을 품은 채 알렌 일행과 함께 구명정으로 보클린데를 탈출한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3246">

--- a/제노사가 데이터베이스.xlsx
+++ b/제노사가 데이터베이스.xlsx
@@ -39192,7 +39192,7 @@
         </x:is>
       </x:c>
       <x:c r="B3245" t="str">
-        <x:v>0x573d7|　A.D. 20XX, 케냐 북부에 위치한 투르카나 호숫가에서 행해진 발굴 조사를 통해 수수께끼의 플레이트 형태를 한 물체가 발견되었다. 훗날 “조하르”라고 호칭되는 그 물체로 인해 로스트 예루살렘은 이 세계에서 소멸하게 되었고 인류는 우주로 탈출할 수밖에 없었다.\n\n　그로부터 4000년이 지난 현재.\n\n　T.C. 4767, 순양함 보클린데를 기함으로 하는 성단 연방군 제117 해병 사단는 행성 아리아드네 소실 사건 조사단의 호위 임무를 맡고 있었다.\n\n　보클린데에는 수수께끼의 적 “그노시스”의 습격에 대비해 벡터사에서 제조된 대그노시스용 안드로이드 “KOS-MOS”가 긴급 배치되어 있었으며, 그 기동 실험을 위해 벡터 제1 개발국 주임 시온 우즈키를 포함한 개발 멤버들도 승선해 있었다.\n\n　함대의 조사 임무가 진행되는 가운데 KOS-MOS의 기동 실험이 반복되지만 뜻대로 진척되지 않아 도저히 실전을 치를 수 있는 상태가 아니었다.\n\n　실험 실패로 고민하는 한편, 이제는 세상을 떠난 연인 “케빈”의 유품이나 다름없는 KOS-MOS가 병기로서 깨어나는 것에 거부감을 느끼는 시온.\n\n　부주임인 알렌 리즐리는 그런 그녀를 짝사랑하며 끊임없이 신경 쓰고 있었으나 그저 묵묵히 지켜볼 수밖에 없었다.\n\n　사건이 발생한 우주 영역을 조사하던 중 보클린데는 “조하르”로 추정되는 물체를 발견하고 회수한다.\n\n　조사를 마치고 우주 영역을 이탈하는 함대. 무사히 임무가 종료된 것에 안도하는 함대 크루들. 하지만 그 직후 조하르를 노리는 “그노시스” 대군이 함대를 습격한다.\n\n　함내에 침입한 그노시스에게 습격당하는 시온. 희미해지는 의식 속에서 그녀는 수수께끼의 소녀 “네피림”의 환영을 본다.\n\n　저항할 힘조차 없이 자신의 죽음을 각오하는 시온. 그런 그녀의 위기를 구한 것은 자율 기동한 KOS-MOS였다.\n\n　KOS-MOS의 도움을 받아 알렌, 버질 일행과 합류한 시온은 그대로 보클린데 탈출을 시도한다.\n\n　차례차례 덤벼드는 그노시스를 가볍게 격퇴하는 KOS-MOS. 하지만 그 전투 중 KOS-MOS는 시온의 목숨을 구하기 위해 그노시스와 함께 버질 중위를 사살하고 만다.\n\n　버질을 죽인 것에 아무런 감정도 느끼지 않는 KOS-MOS는 그 행위를 비난하는 시온을 향해 자신은 병기일 뿐이라고 일축한다.\n\n　그런 KOS-MOS에게 시온은 착잡한 마음을 품은 채 알렌 일행과 함께 구명정으로 보클린데를 탈출한다.</x:v>
+        <x:v>0x573d7|　A.D. 20XX, 케냐 북부에 위치한 투르카나 호숫가에서 행해진 발굴 조사를 통해 수수께끼의 플레이트 형태를 한 물체가 발견되었다. 훗날 “조하르”라고 호칭되는 그 물체로 인해 로스트 예루살렘은 이 세계에서 소멸하게 되었고 인류는 우주로 탈출할 수밖에 없었다.\n\n　그로부터 4000년이 지난 현재.\n\n　T.C. 4767, 순양함 보클린데를 기함으로 하는 성단 연방군 제117 해병 사단는 행성 아리아드네 소실 사건 조사단의 호위 임무를 맡고 있었다.\n\n　보클린데에는 수수께끼의 적 개체 “그노시스”의 습격에 대비해 벡터사에서 제조된 대그노시스용 안드로이드 “KOS-MOS”가 긴급 배치되어 있었으며, 그 기동 실험을 위해 벡터 제1 개발국 주임 시온 우즈키를 포함한 개발 멤버들도 승선해 있었다.\n\n　함대의 조사 임무가 진행되는 가운데 KOS-MOS의 기동 실험이 반복되지만 뜻대로 진척되지 않아 도저히 실전을 치를 수 있는 상태가 아니었다.\n\n　실험 실패로 고민하는 한편, 이제는 세상을 떠난 연인 “케빈”의 유품이나 다름없는 KOS-MOS가 병기로서 깨어나는 것에 거부감을 느끼는 시온.\n\n　부주임인 알렌 리즐리는 그런 그녀를 짝사랑하며 끊임없이 신경 쓰고 있었으나 그저 묵묵히 지켜볼 수밖에 없었다.\n\n　사건이 발생한 우주 영역을 조사하던 중 보클린데는 “조하르”로 추정되는 물체를 발견하고 회수한다.\n\n　조사를 마치고 우주 영역을 이탈하는 함대. 무사히 임무가 종료된 것에 안도하는 함대 크루들. 하지만 그 직후 조하르를 노리는 “그노시스” 대군이 함대를 습격한다.\n\n　함내에 침입한 그노시스에게 습격당하는 시온. 희미해지는 의식 속에서 그녀는 수수께끼의 소녀 “네피림”의 환영을 본다.\n\n　저항할 힘조차 없이 자신의 죽음을 각오하는 시온. 그런 그녀의 위기를 구한 것은 자율 기동한 KOS-MOS였다.\n\n　KOS-MOS의 도움을 받아 알렌, 버질 일행과 합류한 시온은 그대로 보클린데 탈출을 시도한다.\n\n　차례차례 덤벼드는 그노시스를 가볍게 격퇴하는 KOS-MOS. 하지만 그 전투 중 KOS-MOS는 시온의 목숨을 구하기 위해 그노시스와 함께 버질 중위를 사살하고 만다.\n\n　버질을 죽인 것에 아무런 감정도 느끼지 않는 KOS-MOS는 그 행위를 비난하는 시온을 향해 자신은 병기일 뿐이라고 일축한다.\n\n　그런 KOS-MOS에게 시온은 착잡한 마음을 품은 채 알렌 일행과 함께 구명정으로 보클린데를 탈출한다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3246">
